--- a/vtiger-crm-a15-pro/src/test/resources/testScriptData.xlsx
+++ b/vtiger-crm-a15-pro/src/test/resources/testScriptData.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>orgName</t>
   </si>
@@ -69,6 +69,48 @@
   </si>
   <si>
     <t>education</t>
+  </si>
+  <si>
+    <t>lastname</t>
+  </si>
+  <si>
+    <t>chaudhary</t>
+  </si>
+  <si>
+    <t>sharma</t>
+  </si>
+  <si>
+    <t>nagar</t>
+  </si>
+  <si>
+    <t>chaurasiya</t>
+  </si>
+  <si>
+    <t>mahant</t>
+  </si>
+  <si>
+    <t>singh</t>
+  </si>
+  <si>
+    <t>kumar</t>
+  </si>
+  <si>
+    <t>tiwari</t>
+  </si>
+  <si>
+    <t>chaubey</t>
+  </si>
+  <si>
+    <t>pandey</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>7283840504</t>
+  </si>
+  <si>
+    <t>FALSE</t>
   </si>
 </sst>
 </file>
@@ -125,10 +167,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,14 +453,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -432,8 +477,11 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -441,10 +489,15 @@
         <v>15</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="D2" s="1">
+        <v>9876543210</v>
+      </c>
       <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -452,10 +505,15 @@
         <v>15</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="D3" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -465,8 +523,9 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -474,8 +533,9 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -483,8 +543,9 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -492,8 +553,9 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -501,8 +563,9 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -510,8 +573,9 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -519,8 +583,9 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -528,6 +593,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -536,9 +602,68 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
